--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/134.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/134.xlsx
@@ -426,13 +426,13 @@
         <v>-16.95848386151087</v>
       </c>
       <c r="E2">
-        <v>-5.608811486017839</v>
+        <v>-6.168399547619672</v>
       </c>
       <c r="F2">
-        <v>-4.240133722363433</v>
+        <v>-5.082819455720329</v>
       </c>
       <c r="G2">
-        <v>-10.61473904560065</v>
+        <v>-10.06509579080653</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.68876114154144</v>
       </c>
       <c r="E3">
-        <v>-7.192799238316806</v>
+        <v>-7.145902361493373</v>
       </c>
       <c r="F3">
-        <v>-4.786678109219506</v>
+        <v>-5.061484853261227</v>
       </c>
       <c r="G3">
-        <v>-9.185149475922714</v>
+        <v>-9.324943882409517</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.35482814678836</v>
       </c>
       <c r="E4">
-        <v>-8.092688536173045</v>
+        <v>-7.834040214750945</v>
       </c>
       <c r="F4">
-        <v>-5.048656755661474</v>
+        <v>-5.177435580468088</v>
       </c>
       <c r="G4">
-        <v>-9.952308814829104</v>
+        <v>-9.645136536422289</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.99825667825757</v>
       </c>
       <c r="E5">
-        <v>-8.621913179553449</v>
+        <v>-8.811502272358576</v>
       </c>
       <c r="F5">
-        <v>-4.623392811881875</v>
+        <v>-5.124555090575576</v>
       </c>
       <c r="G5">
-        <v>-7.939752038958747</v>
+        <v>-8.874120411962647</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.62273951139832</v>
       </c>
       <c r="E6">
-        <v>-9.198211310243586</v>
+        <v>-9.677024980970604</v>
       </c>
       <c r="F6">
-        <v>-4.414006383476244</v>
+        <v>-5.00795160985531</v>
       </c>
       <c r="G6">
-        <v>-7.888355819461562</v>
+        <v>-9.143807383228294</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.23247242032973</v>
       </c>
       <c r="E7">
-        <v>-9.623928623230668</v>
+        <v>-10.57344546773697</v>
       </c>
       <c r="F7">
-        <v>-4.24374540423964</v>
+        <v>-4.908583141317689</v>
       </c>
       <c r="G7">
-        <v>-7.979885782531331</v>
+        <v>-8.912661783130842</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.82139864379419</v>
       </c>
       <c r="E8">
-        <v>-11.28579254303954</v>
+        <v>-11.26349886549978</v>
       </c>
       <c r="F8">
-        <v>-4.471602768992894</v>
+        <v>-4.990376138670112</v>
       </c>
       <c r="G8">
-        <v>-7.820810758823812</v>
+        <v>-8.462454074154275</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.37643340822601</v>
       </c>
       <c r="E9">
-        <v>-10.83626451372013</v>
+        <v>-11.94212239486724</v>
       </c>
       <c r="F9">
-        <v>-4.450642588599858</v>
+        <v>-5.271968868475568</v>
       </c>
       <c r="G9">
-        <v>-6.911145676633953</v>
+        <v>-8.160168160963423</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.88108083318694</v>
       </c>
       <c r="E10">
-        <v>-11.73139438539431</v>
+        <v>-12.36098812668072</v>
       </c>
       <c r="F10">
-        <v>-4.910580335125839</v>
+        <v>-4.859585209442098</v>
       </c>
       <c r="G10">
-        <v>-7.780359202879457</v>
+        <v>-8.500445894762951</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.33588960975389</v>
       </c>
       <c r="E11">
-        <v>-13.08410391317354</v>
+        <v>-12.76736432718104</v>
       </c>
       <c r="F11">
-        <v>-4.498117152821701</v>
+        <v>-4.909648421797689</v>
       </c>
       <c r="G11">
-        <v>-6.983676418853846</v>
+        <v>-7.57988911774889</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.74605264465884</v>
       </c>
       <c r="E12">
-        <v>-13.49221451921879</v>
+        <v>-13.2887094257881</v>
       </c>
       <c r="F12">
-        <v>-4.410011995859945</v>
+        <v>-4.908182211494734</v>
       </c>
       <c r="G12">
-        <v>-6.540947232250492</v>
+        <v>-7.753643100377539</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.13156167093516</v>
       </c>
       <c r="E13">
-        <v>-14.23180942262553</v>
+        <v>-13.99050968512681</v>
       </c>
       <c r="F13">
-        <v>-4.341742096358224</v>
+        <v>-4.569199359655926</v>
       </c>
       <c r="G13">
-        <v>-5.955877829640635</v>
+        <v>-7.05819679894284</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.53504303211269</v>
       </c>
       <c r="E14">
-        <v>-13.86247161103394</v>
+        <v>-14.90205527507879</v>
       </c>
       <c r="F14">
-        <v>-4.709856144651282</v>
+        <v>-4.438337190831271</v>
       </c>
       <c r="G14">
-        <v>-5.793475707666147</v>
+        <v>-6.883310609739761</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.99665819323934</v>
       </c>
       <c r="E15">
-        <v>-17.14427483828868</v>
+        <v>-15.67751569262627</v>
       </c>
       <c r="F15">
-        <v>-3.991934967667035</v>
+        <v>-4.584371737005601</v>
       </c>
       <c r="G15">
-        <v>-5.517372899145391</v>
+        <v>-6.309377882324012</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.55547644867369</v>
       </c>
       <c r="E16">
-        <v>-16.65181234690254</v>
+        <v>-17.59519310912845</v>
       </c>
       <c r="F16">
-        <v>-3.52990393671418</v>
+        <v>-4.173794747277638</v>
       </c>
       <c r="G16">
-        <v>-4.213203347222742</v>
+        <v>-6.046603330144361</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.24525217481997</v>
       </c>
       <c r="E17">
-        <v>-16.94047539404748</v>
+        <v>-17.45986872035723</v>
       </c>
       <c r="F17">
-        <v>-3.779962376229864</v>
+        <v>-3.763766136770327</v>
       </c>
       <c r="G17">
-        <v>-4.710420802856961</v>
+        <v>-5.74540327589039</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.07936895378054</v>
       </c>
       <c r="E18">
-        <v>-17.08189058035901</v>
+        <v>-17.423717912354</v>
       </c>
       <c r="F18">
-        <v>-3.455526484351617</v>
+        <v>-3.38924300988181</v>
       </c>
       <c r="G18">
-        <v>-4.500595116032413</v>
+        <v>-5.900247422398722</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.05901664542751</v>
       </c>
       <c r="E19">
-        <v>-18.80980229356976</v>
+        <v>-19.07226359010632</v>
       </c>
       <c r="F19">
-        <v>-2.934123048170511</v>
+        <v>-3.149877965168864</v>
       </c>
       <c r="G19">
-        <v>-4.743364041518248</v>
+        <v>-5.598517680858467</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.17793110914977</v>
       </c>
       <c r="E20">
-        <v>-20.62700645726375</v>
+        <v>-19.44444528337472</v>
       </c>
       <c r="F20">
-        <v>-2.964546497773128</v>
+        <v>-3.010807503749869</v>
       </c>
       <c r="G20">
-        <v>-4.58809614518089</v>
+        <v>-6.221949685177399</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.41904145724321</v>
       </c>
       <c r="E21">
-        <v>-20.22691125021207</v>
+        <v>-19.88778741719966</v>
       </c>
       <c r="F21">
-        <v>-2.530247550731195</v>
+        <v>-2.46443541731358</v>
       </c>
       <c r="G21">
-        <v>-4.513532727999885</v>
+        <v>-6.121653397519639</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.75831814587892</v>
       </c>
       <c r="E22">
-        <v>-19.5097277646693</v>
+        <v>-20.5759660267233</v>
       </c>
       <c r="F22">
-        <v>-1.833940136020792</v>
+        <v>-2.184502735783334</v>
       </c>
       <c r="G22">
-        <v>-4.455422722149057</v>
+        <v>-6.599540577750052</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.16712634949703</v>
       </c>
       <c r="E23">
-        <v>-20.79841825540209</v>
+        <v>-20.71454185983202</v>
       </c>
       <c r="F23">
-        <v>-2.549748147760498</v>
+        <v>-2.296352215978935</v>
       </c>
       <c r="G23">
-        <v>-4.281887235526002</v>
+        <v>-6.496817660212007</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.61341149803089</v>
       </c>
       <c r="E24">
-        <v>-20.68558679702697</v>
+        <v>-21.15101429858732</v>
       </c>
       <c r="F24">
-        <v>-1.864017328049039</v>
+        <v>-2.000729427472264</v>
       </c>
       <c r="G24">
-        <v>-5.533717062472772</v>
+        <v>-6.506782402285213</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.0649096524784</v>
       </c>
       <c r="E25">
-        <v>-20.18586516180654</v>
+        <v>-20.5325153186197</v>
       </c>
       <c r="F25">
-        <v>-1.777772684273972</v>
+        <v>-1.890332075333771</v>
       </c>
       <c r="G25">
-        <v>-5.474051100218488</v>
+        <v>-6.787708675656687</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.49317556906318</v>
       </c>
       <c r="E26">
-        <v>-20.80213613256239</v>
+        <v>-21.17518729284026</v>
       </c>
       <c r="F26">
-        <v>-1.475291842039524</v>
+        <v>-1.83384487376947</v>
       </c>
       <c r="G26">
-        <v>-5.856227098363032</v>
+        <v>-7.421698009700355</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.87441552269533</v>
       </c>
       <c r="E27">
-        <v>-21.62277260681039</v>
+        <v>-21.21776853393439</v>
       </c>
       <c r="F27">
-        <v>-1.521766566806187</v>
+        <v>-1.431620312563934</v>
       </c>
       <c r="G27">
-        <v>-6.481264717268511</v>
+        <v>-6.976760689222308</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-13.18920094730167</v>
       </c>
       <c r="E28">
-        <v>-20.08685007762883</v>
+        <v>-21.21794061594668</v>
       </c>
       <c r="F28">
-        <v>-1.476256890063785</v>
+        <v>-1.579039889035745</v>
       </c>
       <c r="G28">
-        <v>-5.935653706941227</v>
+        <v>-7.160396650285681</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-13.42832381813933</v>
       </c>
       <c r="E29">
-        <v>-20.4891823508403</v>
+        <v>-20.92969418841044</v>
       </c>
       <c r="F29">
-        <v>-1.540215965601338</v>
+        <v>-1.539096841240156</v>
       </c>
       <c r="G29">
-        <v>-7.032175911004169</v>
+        <v>-7.362561734732354</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-13.59111351024916</v>
       </c>
       <c r="E30">
-        <v>-19.73757340589122</v>
+        <v>-20.28995213687285</v>
       </c>
       <c r="F30">
-        <v>-1.312994787013433</v>
+        <v>-1.750458925901463</v>
       </c>
       <c r="G30">
-        <v>-6.745446251302352</v>
+        <v>-7.57066593787648</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-13.67848215692409</v>
       </c>
       <c r="E31">
-        <v>-19.74955574811552</v>
+        <v>-20.59145340782953</v>
       </c>
       <c r="F31">
-        <v>-1.397279513513477</v>
+        <v>-1.347932838961308</v>
       </c>
       <c r="G31">
-        <v>-6.769431153734371</v>
+        <v>-7.567702999618833</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-13.69951609529758</v>
       </c>
       <c r="E32">
-        <v>-19.98620021433435</v>
+        <v>-20.2865603098411</v>
       </c>
       <c r="F32">
-        <v>-1.457225148984467</v>
+        <v>-1.686431095869478</v>
       </c>
       <c r="G32">
-        <v>-5.883274255418878</v>
+        <v>-7.676020739118247</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-13.6699897735086</v>
       </c>
       <c r="E33">
-        <v>-18.65553076955045</v>
+        <v>-20.3463678660604</v>
       </c>
       <c r="F33">
-        <v>-1.336496398598258</v>
+        <v>-1.563414394716738</v>
       </c>
       <c r="G33">
-        <v>-6.690113793158973</v>
+        <v>-7.405684900926901</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-13.60203095336722</v>
       </c>
       <c r="E34">
-        <v>-19.59764355905421</v>
+        <v>-19.706739026373</v>
       </c>
       <c r="F34">
-        <v>-1.458166174354047</v>
+        <v>-1.542357295337574</v>
       </c>
       <c r="G34">
-        <v>-5.887472027162674</v>
+        <v>-7.540702190200537</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-13.51271679909935</v>
       </c>
       <c r="E35">
-        <v>-18.92133407990467</v>
+        <v>-20.03631230770323</v>
       </c>
       <c r="F35">
-        <v>-1.057111267921263</v>
+        <v>-1.729078763235208</v>
       </c>
       <c r="G35">
-        <v>-6.144625273016642</v>
+        <v>-6.702243632014863</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-13.41807927581256</v>
       </c>
       <c r="E36">
-        <v>-19.82729153293119</v>
+        <v>-19.02232357874973</v>
       </c>
       <c r="F36">
-        <v>-1.05026315460232</v>
+        <v>-1.229241872385987</v>
       </c>
       <c r="G36">
-        <v>-5.561317080633676</v>
+        <v>-7.186715487322886</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-13.32491934781359</v>
       </c>
       <c r="E37">
-        <v>-17.42694218584746</v>
+        <v>-18.36674998208131</v>
       </c>
       <c r="F37">
-        <v>-1.472303092450223</v>
+        <v>-1.717508127352905</v>
       </c>
       <c r="G37">
-        <v>-5.20258967654379</v>
+        <v>-6.36734553471665</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.23765962656531</v>
       </c>
       <c r="E38">
-        <v>-17.66064314396131</v>
+        <v>-18.6556168105566</v>
       </c>
       <c r="F38">
-        <v>-1.318039544496482</v>
+        <v>-1.421415654528847</v>
       </c>
       <c r="G38">
-        <v>-5.304491578788096</v>
+        <v>-5.992363352028942</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.15660503535595</v>
       </c>
       <c r="E39">
-        <v>-17.67200961372056</v>
+        <v>-18.40506992913422</v>
       </c>
       <c r="F39">
-        <v>-1.050075943569287</v>
+        <v>-1.470202352716724</v>
       </c>
       <c r="G39">
-        <v>-5.554590052097877</v>
+        <v>-5.970762042385197</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.07483333239698</v>
       </c>
       <c r="E40">
-        <v>-16.4675894957965</v>
+        <v>-17.28996943253746</v>
       </c>
       <c r="F40">
-        <v>-1.705285566324598</v>
+        <v>-1.801314885861534</v>
       </c>
       <c r="G40">
-        <v>-4.943767915738029</v>
+        <v>-6.562376393526194</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.98333746214473</v>
       </c>
       <c r="E41">
-        <v>-17.44510136661822</v>
+        <v>-17.54175711583794</v>
       </c>
       <c r="F41">
-        <v>-1.639422074128009</v>
+        <v>-2.032328330419454</v>
       </c>
       <c r="G41">
-        <v>-4.861209531079684</v>
+        <v>-5.935514664028577</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.87384258878177</v>
       </c>
       <c r="E42">
-        <v>-16.2822662255066</v>
+        <v>-16.46235005136963</v>
       </c>
       <c r="F42">
-        <v>-1.400561505163369</v>
+        <v>-1.842873250092582</v>
       </c>
       <c r="G42">
-        <v>-4.388903930628482</v>
+        <v>-5.433043372623536</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.7399703736898</v>
       </c>
       <c r="E43">
-        <v>-15.03629735856217</v>
+        <v>-16.72486116112027</v>
       </c>
       <c r="F43">
-        <v>-1.892484173846244</v>
+        <v>-2.03596652005255</v>
       </c>
       <c r="G43">
-        <v>-3.820854042636018</v>
+        <v>-5.86595679170295</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.5774875926559</v>
       </c>
       <c r="E44">
-        <v>-15.05400369193216</v>
+        <v>-15.62281172661361</v>
       </c>
       <c r="F44">
-        <v>-1.68158183309349</v>
+        <v>-1.898012697892528</v>
       </c>
       <c r="G44">
-        <v>-5.335928519229015</v>
+        <v>-5.618500133733508</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.38624162163433</v>
       </c>
       <c r="E45">
-        <v>-13.56134620341989</v>
+        <v>-15.46226826609368</v>
       </c>
       <c r="F45">
-        <v>-2.031916631820263</v>
+        <v>-1.963027113501247</v>
       </c>
       <c r="G45">
-        <v>-4.484876645811953</v>
+        <v>-5.196759805849133</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-12.17208888296454</v>
       </c>
       <c r="E46">
-        <v>-13.72356972779667</v>
+        <v>-14.63311373223726</v>
       </c>
       <c r="F46">
-        <v>-1.646091260087948</v>
+        <v>-2.064536083407702</v>
       </c>
       <c r="G46">
-        <v>-4.478040369273359</v>
+        <v>-5.640833073941431</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.9415716837029</v>
       </c>
       <c r="E47">
-        <v>-13.9447494552793</v>
+        <v>-14.33217399205752</v>
       </c>
       <c r="F47">
-        <v>-2.053996764941883</v>
+        <v>-2.172351414351668</v>
       </c>
       <c r="G47">
-        <v>-4.169517388286519</v>
+        <v>-5.327721676837162</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.70276194492547</v>
       </c>
       <c r="E48">
-        <v>-11.72538057191212</v>
+        <v>-13.76731931518477</v>
       </c>
       <c r="F48">
-        <v>-2.025634293437431</v>
+        <v>-2.308399991485251</v>
       </c>
       <c r="G48">
-        <v>-4.021195016490553</v>
+        <v>-5.267529337842134</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.46734544651845</v>
       </c>
       <c r="E49">
-        <v>-11.49386233826997</v>
+        <v>-13.40142314383901</v>
       </c>
       <c r="F49">
-        <v>-1.649688859718306</v>
+        <v>-2.275974377870067</v>
       </c>
       <c r="G49">
-        <v>-3.876507623696705</v>
+        <v>-5.696029799717699</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.24094859836917</v>
       </c>
       <c r="E50">
-        <v>-12.23275079973151</v>
+        <v>-12.44461092770636</v>
       </c>
       <c r="F50">
-        <v>-2.021764989298955</v>
+        <v>-2.751211241958352</v>
       </c>
       <c r="G50">
-        <v>-3.665063080103454</v>
+        <v>-5.183934752429996</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.02636773693741</v>
       </c>
       <c r="E51">
-        <v>-11.74617985302935</v>
+        <v>-12.08022726667916</v>
       </c>
       <c r="F51">
-        <v>-2.360499330916923</v>
+        <v>-2.699016640275358</v>
       </c>
       <c r="G51">
-        <v>-3.774175350532293</v>
+        <v>-5.413074161930652</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.82920026834184</v>
       </c>
       <c r="E52">
-        <v>-10.57313753150444</v>
+        <v>-12.57661594502995</v>
       </c>
       <c r="F52">
-        <v>-2.447520154948414</v>
+        <v>-2.509598008114209</v>
       </c>
       <c r="G52">
-        <v>-3.710626118360444</v>
+        <v>-4.901038704462656</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.64656583404838</v>
       </c>
       <c r="E53">
-        <v>-10.44791163977034</v>
+        <v>-11.22886962476313</v>
       </c>
       <c r="F53">
-        <v>-2.172015097186132</v>
+        <v>-2.387245657618513</v>
       </c>
       <c r="G53">
-        <v>-4.048311695002723</v>
+        <v>-5.373748191469649</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.47306223459672</v>
       </c>
       <c r="E54">
-        <v>-8.884465045570161</v>
+        <v>-10.52059817606745</v>
       </c>
       <c r="F54">
-        <v>-2.11855475011166</v>
+        <v>-2.441918734570684</v>
       </c>
       <c r="G54">
-        <v>-4.43755901841915</v>
+        <v>-5.007135067905219</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.30629678033502</v>
       </c>
       <c r="E55">
-        <v>-8.833189134381309</v>
+        <v>-10.258788979788</v>
       </c>
       <c r="F55">
-        <v>-2.323230253097571</v>
+        <v>-2.706310415257007</v>
       </c>
       <c r="G55">
-        <v>-4.662947579823811</v>
+        <v>-5.587440595484066</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.1369796766758</v>
       </c>
       <c r="E56">
-        <v>-9.501252262362879</v>
+        <v>-10.1757231810653</v>
       </c>
       <c r="F56">
-        <v>-2.444798139662815</v>
+        <v>-2.477695922697594</v>
       </c>
       <c r="G56">
-        <v>-3.860189944733638</v>
+        <v>-5.78492456853821</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.956278275221207</v>
       </c>
       <c r="E57">
-        <v>-8.492462221570184</v>
+        <v>-9.493993118528582</v>
       </c>
       <c r="F57">
-        <v>-2.586258441038886</v>
+        <v>-2.17532276822551</v>
       </c>
       <c r="G57">
-        <v>-5.068304017834333</v>
+        <v>-5.690388630118782</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.760130940573116</v>
       </c>
       <c r="E58">
-        <v>-8.247014401880442</v>
+        <v>-9.830481379668528</v>
       </c>
       <c r="F58">
-        <v>-2.109441880313463</v>
+        <v>-2.369172337624234</v>
       </c>
       <c r="G58">
-        <v>-4.759135480467336</v>
+        <v>-5.480639085841638</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.546134021731161</v>
       </c>
       <c r="E59">
-        <v>-8.493920390200653</v>
+        <v>-8.924542040538043</v>
       </c>
       <c r="F59">
-        <v>-1.607986359559171</v>
+        <v>-2.310068323434489</v>
       </c>
       <c r="G59">
-        <v>-5.255167760798495</v>
+        <v>-5.840564907416741</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.315886929768913</v>
       </c>
       <c r="E60">
-        <v>-9.177751664676931</v>
+        <v>-8.74256531253981</v>
       </c>
       <c r="F60">
-        <v>-2.100240375203166</v>
+        <v>-2.333334678676919</v>
       </c>
       <c r="G60">
-        <v>-4.934898964238322</v>
+        <v>-6.315194510836511</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.074101418176394</v>
       </c>
       <c r="E61">
-        <v>-7.011759904438161</v>
+        <v>-8.123885193611885</v>
       </c>
       <c r="F61">
-        <v>-2.425054830984491</v>
+        <v>-2.293783448662853</v>
       </c>
       <c r="G61">
-        <v>-5.495519988040662</v>
+        <v>-6.01027009285086</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.825373959032129</v>
       </c>
       <c r="E62">
-        <v>-7.910218204507975</v>
+        <v>-7.68186537419719</v>
       </c>
       <c r="F62">
-        <v>-2.278060206990316</v>
+        <v>-2.281816853162012</v>
       </c>
       <c r="G62">
-        <v>-5.173705166713649</v>
+        <v>-6.299144986062124</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.573647722034126</v>
       </c>
       <c r="E63">
-        <v>-7.753582817056666</v>
+        <v>-7.97919592059281</v>
       </c>
       <c r="F63">
-        <v>-1.830384783127976</v>
+        <v>-2.575155004371762</v>
       </c>
       <c r="G63">
-        <v>-6.451903488880714</v>
+        <v>-6.696976554061882</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.323933355302481</v>
       </c>
       <c r="E64">
-        <v>-8.04099147690148</v>
+        <v>-8.1208828153448</v>
       </c>
       <c r="F64">
-        <v>-2.169254148632601</v>
+        <v>-2.457999830961231</v>
       </c>
       <c r="G64">
-        <v>-6.487061482507775</v>
+        <v>-6.695864210760687</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.083399041163743</v>
       </c>
       <c r="E65">
-        <v>-6.670734112342529</v>
+        <v>-7.537601777734835</v>
       </c>
       <c r="F65">
-        <v>-2.378511351723395</v>
+        <v>-2.621496361986575</v>
       </c>
       <c r="G65">
-        <v>-6.370003902784685</v>
+        <v>-7.139298543563905</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.857504990205273</v>
       </c>
       <c r="E66">
-        <v>-6.507559608424144</v>
+        <v>-7.699164144906491</v>
       </c>
       <c r="F66">
-        <v>-2.361567096499131</v>
+        <v>-2.45626274451756</v>
       </c>
       <c r="G66">
-        <v>-5.431272230760025</v>
+        <v>-7.113714647636418</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.651079155270356</v>
       </c>
       <c r="E67">
-        <v>-5.715063071659808</v>
+        <v>-7.27177129653657</v>
       </c>
       <c r="F67">
-        <v>-1.887232324512495</v>
+        <v>-2.381777604392634</v>
       </c>
       <c r="G67">
-        <v>-6.553623311120361</v>
+        <v>-7.04248163926792</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.470818404847349</v>
       </c>
       <c r="E68">
-        <v>-5.817827732315871</v>
+        <v>-7.107627699180543</v>
       </c>
       <c r="F68">
-        <v>-1.925825961808924</v>
+        <v>-2.404759829615903</v>
       </c>
       <c r="G68">
-        <v>-5.491113651927892</v>
+        <v>-6.908699183480431</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.319332993255498</v>
       </c>
       <c r="E69">
-        <v>-5.841624863226179</v>
+        <v>-7.434162374451629</v>
       </c>
       <c r="F69">
-        <v>-2.286120221819556</v>
+        <v>-2.655223340791556</v>
       </c>
       <c r="G69">
-        <v>-7.191125133981195</v>
+        <v>-7.353927831965935</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.197255375270057</v>
       </c>
       <c r="E70">
-        <v>-7.014418118680664</v>
+        <v>-6.473867761807076</v>
       </c>
       <c r="F70">
-        <v>-2.341332565950948</v>
+        <v>-2.434933112262875</v>
       </c>
       <c r="G70">
-        <v>-5.41494462016034</v>
+        <v>-7.495496690861789</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.106757731667808</v>
       </c>
       <c r="E71">
-        <v>-6.178013497937956</v>
+        <v>-7.149602124757639</v>
       </c>
       <c r="F71">
-        <v>-2.568694566997328</v>
+        <v>-2.835716314187541</v>
       </c>
       <c r="G71">
-        <v>-5.63865804552213</v>
+        <v>-7.046311940456857</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.043900458553712</v>
       </c>
       <c r="E72">
-        <v>-7.678912809144189</v>
+        <v>-7.425925080231677</v>
       </c>
       <c r="F72">
-        <v>-2.464462753437872</v>
+        <v>-2.887445373390161</v>
       </c>
       <c r="G72">
-        <v>-7.307480878049961</v>
+        <v>-7.272418890243539</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.001638525652785</v>
       </c>
       <c r="E73">
-        <v>-7.589729042037129</v>
+        <v>-7.631495157809873</v>
       </c>
       <c r="F73">
-        <v>-2.535759507429423</v>
+        <v>-2.817478149080104</v>
       </c>
       <c r="G73">
-        <v>-5.77656544105155</v>
+        <v>-6.611617447877314</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.974094604121538</v>
       </c>
       <c r="E74">
-        <v>-8.164818070167218</v>
+        <v>-6.846411732996093</v>
       </c>
       <c r="F74">
-        <v>-2.840260737759299</v>
+        <v>-3.050603930515163</v>
       </c>
       <c r="G74">
-        <v>-4.950326106451326</v>
+        <v>-7.601841345219797</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.947931769833124</v>
       </c>
       <c r="E75">
-        <v>-7.763717541885832</v>
+        <v>-7.504815625919302</v>
       </c>
       <c r="F75">
-        <v>-2.531458623874088</v>
+        <v>-2.910207252884286</v>
       </c>
       <c r="G75">
-        <v>-5.687111190034903</v>
+        <v>-6.915124952372157</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.908930807301418</v>
       </c>
       <c r="E76">
-        <v>-7.471060380666127</v>
+        <v>-7.74712068464772</v>
       </c>
       <c r="F76">
-        <v>-2.727070959105969</v>
+        <v>-2.914896640751534</v>
       </c>
       <c r="G76">
-        <v>-5.158178708134467</v>
+        <v>-6.80423160844319</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.84649355603995</v>
       </c>
       <c r="E77">
-        <v>-7.626808187211934</v>
+        <v>-7.83956948151431</v>
       </c>
       <c r="F77">
-        <v>-2.78208449506069</v>
+        <v>-3.259279619689192</v>
       </c>
       <c r="G77">
-        <v>-6.026117674347351</v>
+        <v>-6.59619030566431</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.750860231399903</v>
       </c>
       <c r="E78">
-        <v>-8.416397443663344</v>
+        <v>-9.135573457769489</v>
       </c>
       <c r="F78">
-        <v>-3.20613570896259</v>
+        <v>-3.456089774185521</v>
       </c>
       <c r="G78">
-        <v>-5.091060707871283</v>
+        <v>-6.204307787998623</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.616368826850557</v>
       </c>
       <c r="E79">
-        <v>-9.619332222112883</v>
+        <v>-8.909883370175214</v>
       </c>
       <c r="F79">
-        <v>-3.271535315413611</v>
+        <v>-3.541655156690293</v>
       </c>
       <c r="G79">
-        <v>-5.916955745735422</v>
+        <v>-6.804205124078876</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.443239496482255</v>
       </c>
       <c r="E80">
-        <v>-9.815084568042449</v>
+        <v>-10.30610700469415</v>
       </c>
       <c r="F80">
-        <v>-3.560454126529425</v>
+        <v>-3.378311045267064</v>
       </c>
       <c r="G80">
-        <v>-5.225806532410699</v>
+        <v>-6.191525771671497</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.235006872952607</v>
       </c>
       <c r="E81">
-        <v>-10.28032187369447</v>
+        <v>-10.80665282218397</v>
       </c>
       <c r="F81">
-        <v>-3.416611440502902</v>
+        <v>-3.658797904589782</v>
       </c>
       <c r="G81">
-        <v>-5.85751159003227</v>
+        <v>-6.55299099692236</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.997591332647155</v>
       </c>
       <c r="E82">
-        <v>-12.50280634717893</v>
+        <v>-11.18023834239476</v>
       </c>
       <c r="F82">
-        <v>-3.736261853895175</v>
+        <v>-3.543405497012408</v>
       </c>
       <c r="G82">
-        <v>-4.816460887025356</v>
+        <v>-5.940970443077296</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.739130678220764</v>
       </c>
       <c r="E83">
-        <v>-12.32214740511693</v>
+        <v>-12.74296943770172</v>
       </c>
       <c r="F83">
-        <v>-3.672975412688696</v>
+        <v>-3.897549129057253</v>
       </c>
       <c r="G83">
-        <v>-5.243935079783748</v>
+        <v>-6.062474085459627</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.469154770619586</v>
       </c>
       <c r="E84">
-        <v>-12.98952220504933</v>
+        <v>-13.76076661329567</v>
       </c>
       <c r="F84">
-        <v>-3.498724187672806</v>
+        <v>-4.124701553150725</v>
       </c>
       <c r="G84">
-        <v>-5.289309416944999</v>
+        <v>-5.729042559835312</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.196963192427612</v>
       </c>
       <c r="E85">
-        <v>-14.03378378274411</v>
+        <v>-14.72673993234584</v>
       </c>
       <c r="F85">
-        <v>-3.812923943554658</v>
+        <v>-4.151882772738785</v>
       </c>
       <c r="G85">
-        <v>-5.200427890306646</v>
+        <v>-5.41299470883771</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.933571811153859</v>
       </c>
       <c r="E86">
-        <v>-15.21010924792458</v>
+        <v>-15.8584870993948</v>
       </c>
       <c r="F86">
-        <v>-3.927816845588144</v>
+        <v>-3.941891636129111</v>
       </c>
       <c r="G86">
-        <v>-4.5661538493466</v>
+        <v>-5.271167627389793</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.693297496899412</v>
       </c>
       <c r="E87">
-        <v>-17.0453412666431</v>
+        <v>-16.88337586528477</v>
       </c>
       <c r="F87">
-        <v>-4.548107468845845</v>
+        <v>-4.257909658460108</v>
       </c>
       <c r="G87">
-        <v>-4.20535404374913</v>
+        <v>-4.957116035352371</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.490161861600274</v>
       </c>
       <c r="E88">
-        <v>-17.18129511330138</v>
+        <v>-18.80851167847757</v>
       </c>
       <c r="F88">
-        <v>-4.416960341634627</v>
+        <v>-4.587724968252134</v>
       </c>
       <c r="G88">
-        <v>-5.139642963660087</v>
+        <v>-4.870810113143571</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.340215297344311</v>
       </c>
       <c r="E89">
-        <v>-18.85637764873865</v>
+        <v>-20.12010719074116</v>
       </c>
       <c r="F89">
-        <v>-4.602226368005542</v>
+        <v>-4.617128697581905</v>
       </c>
       <c r="G89">
-        <v>-4.103299856410017</v>
+        <v>-4.765862509003135</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.261256777045983</v>
       </c>
       <c r="E90">
-        <v>-21.76251678621308</v>
+        <v>-21.78917591269624</v>
       </c>
       <c r="F90">
-        <v>-4.468194037130374</v>
+        <v>-4.87730398818798</v>
       </c>
       <c r="G90">
-        <v>-5.082102371642015</v>
+        <v>-4.691216328183648</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.266205593588851</v>
       </c>
       <c r="E91">
-        <v>-23.17578559689689</v>
+        <v>-24.02668586293815</v>
       </c>
       <c r="F91">
-        <v>-4.75113617743499</v>
+        <v>-4.760432944796609</v>
       </c>
       <c r="G91">
-        <v>-5.121775949384641</v>
+        <v>-5.151584101420239</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.366441607461533</v>
       </c>
       <c r="E92">
-        <v>-25.17637937247951</v>
+        <v>-25.83051744288749</v>
       </c>
       <c r="F92">
-        <v>-4.933669419744069</v>
+        <v>-5.183082561052973</v>
       </c>
       <c r="G92">
-        <v>-5.318379317325339</v>
+        <v>-4.993727358471171</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.5692691994892</v>
       </c>
       <c r="E93">
-        <v>-26.53547404860955</v>
+        <v>-27.15966532040481</v>
       </c>
       <c r="F93">
-        <v>-5.27857095667588</v>
+        <v>-5.364849563514462</v>
       </c>
       <c r="G93">
-        <v>-5.290981242442331</v>
+        <v>-5.583947969940134</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.871099512927062</v>
       </c>
       <c r="E94">
-        <v>-28.86596262717694</v>
+        <v>-29.94611915409352</v>
       </c>
       <c r="F94">
-        <v>-5.716782282961235</v>
+        <v>-5.449031572456559</v>
       </c>
       <c r="G94">
-        <v>-5.689431882457932</v>
+        <v>-5.601331644566847</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.263734040120842</v>
       </c>
       <c r="E95">
-        <v>-32.49808860366506</v>
+        <v>-32.40096642162256</v>
       </c>
       <c r="F95">
-        <v>-5.449894731290276</v>
+        <v>-5.814422777096616</v>
       </c>
       <c r="G95">
-        <v>-4.775274389971282</v>
+        <v>-5.396723377512192</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.734944148050363</v>
       </c>
       <c r="E96">
-        <v>-34.23965140177193</v>
+        <v>-34.81858284009753</v>
       </c>
       <c r="F96">
-        <v>-5.423692641972325</v>
+        <v>-5.820804519567783</v>
       </c>
       <c r="G96">
-        <v>-5.268856866603381</v>
+        <v>-6.358138907571937</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.252842674203102</v>
       </c>
       <c r="E97">
-        <v>-36.69465943012824</v>
+        <v>-36.63695082161149</v>
       </c>
       <c r="F97">
-        <v>-5.727994235758127</v>
+        <v>-6.154814681887586</v>
       </c>
       <c r="G97">
-        <v>-5.609737119691057</v>
+        <v>-6.624723897667288</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.802087215419612</v>
       </c>
       <c r="E98">
-        <v>-38.11612251452893</v>
+        <v>-39.65733203711444</v>
       </c>
       <c r="F98">
-        <v>-5.931176192316789</v>
+        <v>-6.259024129527166</v>
       </c>
       <c r="G98">
-        <v>-6.807608364893246</v>
+        <v>-7.047510357942072</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.341142362290586</v>
       </c>
       <c r="E99">
-        <v>-41.38441277534477</v>
+        <v>-41.96160754388843</v>
       </c>
       <c r="F99">
-        <v>-6.066926557185364</v>
+        <v>-6.475957813339703</v>
       </c>
       <c r="G99">
-        <v>-7.049046451072295</v>
+        <v>-7.405562410741948</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.870186761317048</v>
       </c>
       <c r="E100">
-        <v>-43.3368937788329</v>
+        <v>-44.80050789929697</v>
       </c>
       <c r="F100">
-        <v>-6.386260948413469</v>
+        <v>-6.658192429200073</v>
       </c>
       <c r="G100">
-        <v>-6.625127784223079</v>
+        <v>-7.947084897328232</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.332091481169583</v>
       </c>
       <c r="E101">
-        <v>-47.80571646263722</v>
+        <v>-47.51159886855004</v>
       </c>
       <c r="F101">
-        <v>-6.365997010822486</v>
+        <v>-6.67368165708132</v>
       </c>
       <c r="G101">
-        <v>-7.948713685733553</v>
+        <v>-8.593114685498229</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.782960917560555</v>
       </c>
       <c r="E102">
-        <v>-49.86771068517134</v>
+        <v>-49.45499122470477</v>
       </c>
       <c r="F102">
-        <v>-7.056957728131519</v>
+        <v>-6.820232276147595</v>
       </c>
       <c r="G102">
-        <v>-8.64988723095119</v>
+        <v>-8.650380502236542</v>
       </c>
     </row>
   </sheetData>
